--- a/deploy_app/sample_data/projects/rev_019/engagement_workbook.xlsx
+++ b/deploy_app/sample_data/projects/rev_019/engagement_workbook.xlsx
@@ -507,25 +507,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Customer 10</t>
+          <t>Customer 26</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>287631.02</v>
+        <v>134684.04</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -547,30 +547,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Customer 37</t>
+          <t>Customer 5</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>391976.9</v>
+        <v>32192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -587,20 +587,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Customer 27</t>
+          <t>Customer 5</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>139426.95</v>
+        <v>493207.25</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -627,25 +627,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Customer 31</t>
+          <t>Customer 12</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28358.18</v>
+        <v>386796.31</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>02/01/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>02/01/2025</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -667,30 +667,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Customer 39</t>
+          <t>Customer 27</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>343598.3</v>
+        <v>193485.85</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -707,11 +707,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Customer 22</t>
+          <t>Customer 25</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>348351.74</v>
+        <v>194066.31</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -747,30 +747,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Customer 18</t>
+          <t>Customer 9</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>449545.37</v>
+        <v>330231.71</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -787,25 +787,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Customer 20</t>
+          <t>Customer 35</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>162365.16</v>
+        <v>202598.73</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -827,30 +827,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Customer 15</t>
+          <t>Customer 1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>75848.91</v>
+        <v>380527.91</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -867,30 +867,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Customer 27</t>
+          <t>Customer 35</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>306439.77</v>
+        <v>217822.73</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -907,30 +907,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Customer 27</t>
+          <t>Customer 23</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>373062.95</v>
+        <v>86009.47</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>02/01/2025</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -947,30 +947,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Customer 33</t>
+          <t>Customer 3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>397830.29</v>
+        <v>406644.31</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -987,30 +987,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Customer 26</t>
+          <t>Customer 2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>76468.41</v>
+        <v>127926.48</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1027,30 +1027,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Customer 13</t>
+          <t>Customer 29</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>420118.57</v>
+        <v>302914.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1067,25 +1067,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Customer 24</t>
+          <t>Customer 26</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>355270.63</v>
+        <v>225091.78</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1107,26 +1107,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Customer 33</t>
+          <t>Customer 50</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>204501.72</v>
+        <v>37657.58</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1143,30 +1143,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Customer 32</t>
+          <t>Customer 47</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>301081.36</v>
+        <v>292294.06</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1183,30 +1183,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Customer 23</t>
+          <t>Customer 21</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>178682.01</v>
+        <v>126082.98</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1223,25 +1223,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Customer 6</t>
+          <t>Customer 27</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>149683.99</v>
+        <v>157245.47</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1263,30 +1263,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Customer 37</t>
+          <t>Customer 48</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>392116.77</v>
+        <v>456673.06</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1303,30 +1303,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Customer 44</t>
+          <t>Customer 32</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>111298.18</v>
+        <v>32973.21</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1343,30 +1343,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Customer 50</t>
+          <t>Customer 34</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>483897.79</v>
+        <v>166179.88</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1383,25 +1383,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Customer 9</t>
+          <t>Customer 25</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>327212.06</v>
+        <v>100100.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1423,15 +1423,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Customer 39</t>
+          <t>Customer 15</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>404491.93</v>
+        <v>157360.85</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1463,25 +1463,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Customer 42</t>
+          <t>Customer 36</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>144935.49</v>
+        <v>212211.97</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>28/12/2024</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>30/12/2024</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>02/01/2025</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1503,11 +1503,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Customer 14</t>
+          <t>Customer 25</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>238682.03</v>
+        <v>129000.67</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1543,30 +1543,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Customer 26</t>
+          <t>Customer 29</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>296398.71</v>
+        <v>425095.36</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1583,25 +1583,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Customer 24</t>
+          <t>Customer 13</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>285113.99</v>
+        <v>35252.95</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1623,25 +1623,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Customer 44</t>
+          <t>Customer 3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62971.22</v>
+        <v>438074.02</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>04/01/2025</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>07/01/2025</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1663,25 +1663,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Customer 41</t>
+          <t>Customer 36</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>169317.16</v>
+        <v>116338.1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>29/12/2024</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1703,25 +1703,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Customer 42</t>
+          <t>Customer 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>156407.64</v>
+        <v>113785.81</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1743,25 +1743,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Customer 4</t>
+          <t>Customer 49</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>404660.61</v>
+        <v>244671.23</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1783,30 +1783,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Customer 44</t>
+          <t>Customer 14</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>78565.46000000001</v>
+        <v>204349.71</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1827,21 +1827,21 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>137118.87</v>
+        <v>196524.25</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>29/12/2024</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>26/12/2024</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1863,25 +1863,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Customer 3</t>
+          <t>Customer 17</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>295681.61</v>
+        <v>186225.86</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>06/01/2025</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>03/01/2025</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1903,30 +1903,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Customer 46</t>
+          <t>Customer 31</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>118957.97</v>
+        <v>383198.19</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>02/01/2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>04/01/2025</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>05/01/2025</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1943,30 +1943,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Customer 43</t>
+          <t>Customer 27</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>185663.59</v>
+        <v>32400.57</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1983,25 +1983,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Customer 36</t>
+          <t>Customer 17</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>98756.57000000001</v>
+        <v>281122.67</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2023,30 +2023,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Customer 17</t>
+          <t>Customer 19</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>365341.45</v>
+        <v>84681.59</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2063,30 +2063,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Customer 22</t>
+          <t>Customer 16</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>330672.98</v>
+        <v>254657.73</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2103,30 +2103,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Customer 20</t>
+          <t>Customer 49</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>216031.56</v>
+        <v>412580.05</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2143,30 +2143,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Customer 19</t>
+          <t>Customer 11</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>237242.71</v>
+        <v>369058.4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2183,25 +2183,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Customer 38</t>
+          <t>Customer 35</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>294353.42</v>
+        <v>249275</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2223,25 +2223,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Customer 13</t>
+          <t>Customer 34</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>255233.91</v>
+        <v>26573.64</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2267,26 +2267,26 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>36490.37</v>
+        <v>77370.85000000001</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2303,30 +2303,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Customer 22</t>
+          <t>Customer 1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>210504</v>
+        <v>117172.64</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2343,30 +2343,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Customer 46</t>
+          <t>Customer 43</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>98374.82000000001</v>
+        <v>467612.82</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>02/01/2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>04/01/2025</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>06/01/2025</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2383,30 +2383,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Customer 12</t>
+          <t>Customer 1</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>163572.9</v>
+        <v>270784.12</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>02/01/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>02/01/2025</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2423,25 +2423,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Customer 14</t>
+          <t>Customer 18</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>382984.71</v>
+        <v>272511.67</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>02/01/2025</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2463,15 +2463,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Customer 32</t>
+          <t>Customer 45</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>394753.34</v>
+        <v>340276.15</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2503,25 +2503,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Customer 41</t>
+          <t>Customer 34</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>220410.76</v>
+        <v>82959.77</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>29/12/2024</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>28/12/2024</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2543,30 +2543,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Customer 3</t>
+          <t>Customer 23</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>271553.48</v>
+        <v>140989.12</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>29/12/2024</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>01/01/2025</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2583,30 +2583,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Customer 49</t>
+          <t>Customer 26</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>418282.05</v>
+        <v>234908.9</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>02/01/2025</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>01/01/2025</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>31/12/2024</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2623,11 +2623,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Customer 41</t>
+          <t>Customer 44</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>369465.59</v>
+        <v>415750.42</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2663,25 +2663,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Customer 20</t>
+          <t>Customer 42</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>73176.09</v>
+        <v>382197.07</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2703,30 +2703,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Customer 11</t>
+          <t>Customer 36</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>41990.64</v>
+        <v>243242.5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2743,30 +2743,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Customer 30</t>
+          <t>Customer 6</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>366637.64</v>
+        <v>254930.61</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2783,25 +2783,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Customer 44</t>
+          <t>Customer 37</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>497781.48</v>
+        <v>488891.32</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>04/01/2025</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>07/01/2025</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2823,25 +2823,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Customer 13</t>
+          <t>Customer 15</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>90792.92</v>
+        <v>113594.36</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2863,25 +2863,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Customer 47</t>
+          <t>Customer 5</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>492590.97</v>
+        <v>345370.08</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2903,25 +2903,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Customer 11</t>
+          <t>Customer 3</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>70349.37</v>
+        <v>97883.71000000001</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>02/01/2025</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2943,30 +2943,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Customer 41</t>
+          <t>Customer 38</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>135336.7</v>
+        <v>80653.87</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2983,25 +2983,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Customer 43</t>
+          <t>Customer 37</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>62975.59</v>
+        <v>127831.38</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>02/01/2025</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3023,30 +3023,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Customer 27</t>
+          <t>Customer 22</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>227714</v>
+        <v>198084.64</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3063,25 +3063,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Customer 45</t>
+          <t>Customer 33</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>85032.28</v>
+        <v>375273.72</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3103,30 +3103,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Customer 43</t>
+          <t>Customer 5</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>59480.13</v>
+        <v>176890.45</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3143,25 +3143,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Customer 45</t>
+          <t>Customer 50</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>77210.13</v>
+        <v>169924.56</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3183,30 +3183,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Customer 8</t>
+          <t>Customer 29</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>148526.32</v>
+        <v>250395.69</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Customer 13</t>
+          <t>Customer 28</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>391199.87</v>
+        <v>101011.54</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3263,25 +3263,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Customer 27</t>
+          <t>Customer 50</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>154722.09</v>
+        <v>313121.79</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>07/01/2025</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>04/01/2025</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3303,25 +3303,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Customer 14</t>
+          <t>Customer 10</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>347219.92</v>
+        <v>196200</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3343,25 +3343,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Customer 1</t>
+          <t>Customer 21</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>339100.23</v>
+        <v>186743.11</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3383,11 +3383,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Customer 10</t>
+          <t>Customer 29</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>475228.55</v>
+        <v>186359.57</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3423,30 +3423,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Customer 7</t>
+          <t>Customer 12</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>453341.9</v>
+        <v>221179.96</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3463,15 +3463,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Customer 19</t>
+          <t>Customer 7</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>139421.26</v>
+        <v>22868.33</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3503,25 +3503,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Customer 3</t>
+          <t>Customer 21</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>427601.86</v>
+        <v>433221.91</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3543,25 +3543,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Customer 48</t>
+          <t>Customer 50</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>66791.52</v>
+        <v>51502.76</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3583,30 +3583,30 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Customer 43</t>
+          <t>Customer 11</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>327127.33</v>
+        <v>345804.84</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3623,25 +3623,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Customer 40</t>
+          <t>Customer 18</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>141471.61</v>
+        <v>251630.73</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3663,11 +3663,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Customer 12</t>
+          <t>Customer 27</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>65777.67999999999</v>
+        <v>156878.6</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3703,30 +3703,30 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Customer 25</t>
+          <t>Customer 16</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>348052.19</v>
+        <v>363240.73</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3743,11 +3743,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Customer 11</t>
+          <t>Customer 30</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>65397.71</v>
+        <v>62416.46</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3783,25 +3783,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Customer 38</t>
+          <t>Customer 22</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>246510.68</v>
+        <v>422390.56</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3823,25 +3823,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Customer 40</t>
+          <t>Customer 28</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>196077.88</v>
+        <v>409582.98</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3863,30 +3863,30 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Customer 47</t>
+          <t>Customer 21</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>486987.84</v>
+        <v>305573.52</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3903,25 +3903,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Customer 8</t>
+          <t>Customer 26</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>444921.02</v>
+        <v>484675.36</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>30/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>28/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3943,20 +3943,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Customer 21</t>
+          <t>Customer 32</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>16056.5</v>
+        <v>484203.91</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>30/12/2024</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>02/01/2025</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3983,30 +3983,30 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Customer 37</t>
+          <t>Customer 26</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>364649.04</v>
+        <v>188857.61</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>05/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4023,30 +4023,30 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Customer 34</t>
+          <t>Customer 35</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>266320.56</v>
+        <v>98164.33</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4063,25 +4063,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Customer 47</t>
+          <t>Customer 30</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>131802.73</v>
+        <v>472057.71</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>03/01/2025</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>04/01/2025</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>05/01/2025</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4103,25 +4103,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Customer 25</t>
+          <t>Customer 45</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>82840.67999999999</v>
+        <v>43887.75</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>29/12/2024</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>31/12/2024</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
-        </is>
-      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4143,30 +4143,30 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Customer 11</t>
+          <t>Customer 41</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>257728.11</v>
+        <v>158387.99</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>04/01/2025</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4183,30 +4183,30 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Customer 5</t>
+          <t>Customer 28</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>378200.7</v>
+        <v>396647.61</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>30/12/2024</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>02/01/2025</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>04/01/2025</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4223,25 +4223,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Customer 18</t>
+          <t>Customer 31</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>34671.85</v>
+        <v>295299.57</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>29/12/2024</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4263,30 +4263,30 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Customer 26</t>
+          <t>Customer 45</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>410380.62</v>
+        <v>214967.34</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4303,25 +4303,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Customer 37</t>
+          <t>Customer 35</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>229568.31</v>
+        <v>300971.77</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>29/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4343,30 +4343,30 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Customer 32</t>
+          <t>Customer 43</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>375167.09</v>
+        <v>335700</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>02/01/2025</t>
+          <t>27/12/2024</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4383,25 +4383,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Customer 3</t>
+          <t>Customer 37</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>282994.2</v>
+        <v>491968.02</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>31/12/2024</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>28/12/2024</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4423,30 +4423,30 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Customer 40</t>
+          <t>Customer 49</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>322393.68</v>
+        <v>172482.38</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>27/12/2024</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P01-2025</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4463,30 +4463,30 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Customer 43</t>
+          <t>Customer 15</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>233541.88</v>
+        <v>260231.36</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>02/01/2025</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>03/01/2025</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>P01-2025</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4506,7 +4506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4573,11 +4573,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SO-2024-0044</t>
+          <t>SO-2024-0067</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>255233.91</v>
+        <v>169924.56</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4601,20 +4601,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SO-2024-0047</t>
+          <t>SO-2024-0072</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>98374.82000000001</v>
+        <v>186743.11</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>04/01/2025</t>
+          <t>05/01/2025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4629,20 +4629,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SO-2024-0007</t>
+          <t>SO-2024-0075</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>449545.37</v>
+        <v>22868.33</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>03/01/2025</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SO-2024-0029</t>
+          <t>SO-2024-0089</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>62971.22</v>
+        <v>98164.33</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4685,583 +4685,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SO-2024-0059</t>
+          <t>SO-2024-0074</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>90792.92</v>
+        <v>221179.96</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31/12/2024</t>
+          <t>30/12/2024</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SO-2024-0043</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>294353.42</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>27/12/2024</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>24/12/2024</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SO-2024-0072</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>339100.23</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>02/01/2025</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>02/01/2025</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SO-2024-0080</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>65777.67999999999</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>27/12/2024</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>27/12/2024</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SO-2024-0077</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>66791.52</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>31/12/2024</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>31/12/2024</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SO-2024-0061</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>70349.37</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>29/12/2024</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>26/12/2024</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SO-2024-0085</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>486987.84</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>31/12/2024</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>28/12/2024</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SO-2024-0099</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>322393.68</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>26/12/2024</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>26/12/2024</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SO-2024-0058</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>497781.48</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>04/01/2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>04/01/2025</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SO-2024-0015</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>355270.63</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>29/12/2024</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>29/12/2024</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SO-2024-0013</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>76468.41</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>27/12/2024</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>27/12/2024</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SO-2024-0090</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>131802.73</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>04/01/2025</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>04/01/2025</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SO-2024-0097</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>375167.09</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>02/01/2025</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>02/01/2025</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>18</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SO-2024-0001</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>287631.02</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>01/01/2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>01/01/2025</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>19</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SO-2024-0100</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>233541.88</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>20</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SO-2024-0046</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>210504</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>28/12/2024</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>28/12/2024</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>21</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SO-2024-0038</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>98756.57000000001</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>30/12/2024</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>30/12/2024</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>22</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SO-2024-0071</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>347219.92</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>26/12/2024</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>26/12/2024</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>23</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SO-2024-0067</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>77210.13</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>24</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SO-2024-0048</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>163572.9</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>27/12/2024</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>27/12/2024</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SO-2024-0014</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>420118.57</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>03/01/2025</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>02/01/2025</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
